--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:53</t>
+    <t xml:space="preserve">2026-09-09 19:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:18</t>
+    <t xml:space="preserve">2026-09-17 03:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:51</t>
+    <t xml:space="preserve">2026-09-27 02:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:13</t>
+    <t xml:space="preserve">2026-10-02 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
+++ b/output/graficos_envejecimiento/plot_regional_d_enveje_a_2020_los_rios.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 23:04</t>
+    <t xml:space="preserve">2026-10-05 05:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Los Rios</t>
+    <t xml:space="preserve">Region de Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
